--- a/2x2 presencial.xlsx
+++ b/2x2 presencial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edd\Desktop\Codes\Liga preconauta\preconauta-league\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AECC94-D0D6-4433-8E56-93E566876930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E905F191-E8D9-4CE7-A701-0FC8E1A1ECCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="297">
   <si>
     <t>evento</t>
   </si>
@@ -867,12 +867,6 @@
     <t>Rogério</t>
   </si>
   <si>
-    <t>Metuda &amp; Rudzzt</t>
-  </si>
-  <si>
-    <t>Metuda</t>
-  </si>
-  <si>
     <t>Host of Mordor</t>
   </si>
   <si>
@@ -934,6 +928,9 @@
   </si>
   <si>
     <t>silverquill Statement</t>
+  </si>
+  <si>
+    <t>counter intelligence</t>
   </si>
 </sst>
 </file>
@@ -4908,7 +4905,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B172" t="s">
         <v>273</v>
@@ -4923,12 +4920,12 @@
         <v>254</v>
       </c>
       <c r="F172" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B173" t="s">
         <v>38</v>
@@ -4948,7 +4945,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B174" t="s">
         <v>146</v>
@@ -4960,7 +4957,7 @@
         <v>274</v>
       </c>
       <c r="E174" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c r="F174" t="s">
         <v>163</v>
@@ -4968,13 +4965,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B175" t="s">
-        <v>275</v>
+        <v>132</v>
       </c>
       <c r="C175" t="s">
-        <v>276</v>
+        <v>169</v>
       </c>
       <c r="D175" t="s">
         <v>170</v>
@@ -4988,7 +4985,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B176" t="s">
         <v>143</v>
@@ -5003,21 +5000,21 @@
         <v>130</v>
       </c>
       <c r="F176" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B177" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C177" t="s">
         <v>168</v>
       </c>
       <c r="D177" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E177" t="s">
         <v>17</v>
@@ -5028,7 +5025,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B178" t="s">
         <v>201</v>
@@ -5043,12 +5040,12 @@
         <v>126</v>
       </c>
       <c r="F178" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B179" t="s">
         <v>260</v>
@@ -5060,7 +5057,7 @@
         <v>262</v>
       </c>
       <c r="E179" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="F179" t="s">
         <v>27</v>
@@ -5068,7 +5065,7 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B180" t="s">
         <v>189</v>
@@ -5088,16 +5085,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B181" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C181" t="s">
         <v>235</v>
       </c>
       <c r="D181" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E181" t="s">
         <v>162</v>
@@ -5108,19 +5105,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B182" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C182" t="s">
         <v>222</v>
       </c>
       <c r="D182" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E182" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F182" t="s">
         <v>178</v>
@@ -5128,7 +5125,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>38</v>
@@ -5148,7 +5145,7 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>10</v>
@@ -5160,7 +5157,7 @@
         <v>160</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F184" t="s">
         <v>48</v>
@@ -5168,7 +5165,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>84</v>
@@ -5188,10 +5185,10 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>187</v>
@@ -5203,24 +5200,24 @@
         <v>87</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>194</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>29</v>
@@ -5228,16 +5225,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>17</v>
@@ -5248,33 +5245,33 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>227</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>163</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>165</v>
@@ -5288,13 +5285,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>179</v>

--- a/2x2 presencial.xlsx
+++ b/2x2 presencial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edd\Desktop\Codes\Liga preconauta\preconauta-league\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E905F191-E8D9-4CE7-A701-0FC8E1A1ECCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1DFEA5-4A27-4B7E-A9B4-47F6025EE192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="376">
   <si>
     <t>evento</t>
   </si>
@@ -270,9 +270,6 @@
     <t>Matheus &amp; Romano</t>
   </si>
   <si>
-    <t>World Shapper</t>
-  </si>
-  <si>
     <t>Explorers of the Deep</t>
   </si>
   <si>
@@ -411,9 +408,6 @@
     <t>Rogério &amp; Nathan</t>
   </si>
   <si>
-    <t>Zangalli  &amp; Clausius</t>
-  </si>
-  <si>
     <t>liga-2x2-presencial-s2-e5</t>
   </si>
   <si>
@@ -597,9 +591,6 @@
     <t>Lucas Alano</t>
   </si>
   <si>
-    <t>iga-2x2-presencial-s3-e01</t>
-  </si>
-  <si>
     <t>André &amp; Beck</t>
   </si>
   <si>
@@ -654,9 +645,6 @@
     <t>Susan</t>
   </si>
   <si>
-    <t>Turtle Power</t>
-  </si>
-  <si>
     <t>Rafael &amp; Beatriz</t>
   </si>
   <si>
@@ -675,9 +663,6 @@
     <t>Pedro</t>
   </si>
   <si>
-    <t>Mind Flayers</t>
-  </si>
-  <si>
     <t>Luiz &amp; João</t>
   </si>
   <si>
@@ -867,9 +852,6 @@
     <t>Rogério</t>
   </si>
   <si>
-    <t>Host of Mordor</t>
-  </si>
-  <si>
     <t>Sonia &amp; Denilson</t>
   </si>
   <si>
@@ -909,12 +891,6 @@
     <t>Rogerio</t>
   </si>
   <si>
-    <t>Peludinho &amp; Zangas</t>
-  </si>
-  <si>
-    <t>Peludinho</t>
-  </si>
-  <si>
     <t>Lucas &amp; Castanhari</t>
   </si>
   <si>
@@ -927,10 +903,271 @@
     <t>Maestros Massacre</t>
   </si>
   <si>
-    <t>silverquill Statement</t>
-  </si>
-  <si>
-    <t>counter intelligence</t>
+    <t>liga-2x2-presencial-s3-e8</t>
+  </si>
+  <si>
+    <t>Quintana</t>
+  </si>
+  <si>
+    <t>rogerio &amp; Beck</t>
+  </si>
+  <si>
+    <t>rogerio</t>
+  </si>
+  <si>
+    <t>liga-2x2-presencial-s3-e9</t>
+  </si>
+  <si>
+    <t>Legado das Lendas</t>
+  </si>
+  <si>
+    <t>Zanga &amp; Beck</t>
+  </si>
+  <si>
+    <t>Zanga</t>
+  </si>
+  <si>
+    <t>Donia &amp; Senilson</t>
+  </si>
+  <si>
+    <t>Donia</t>
+  </si>
+  <si>
+    <t>Senilson</t>
+  </si>
+  <si>
+    <t>Gus &amp; Gustavo Dias</t>
+  </si>
+  <si>
+    <t>Gus</t>
+  </si>
+  <si>
+    <t>Gustavo Dias</t>
+  </si>
+  <si>
+    <t>liga-2x2-presencial-s3-e10</t>
+  </si>
+  <si>
+    <t>Oscar &amp; Chueiry</t>
+  </si>
+  <si>
+    <t>Beck &amp; Zanga</t>
+  </si>
+  <si>
+    <t>Matheus Diogo &amp; Pedro Diogo</t>
+  </si>
+  <si>
+    <t>Matheus Diogo</t>
+  </si>
+  <si>
+    <t>Pedro Diogo</t>
+  </si>
+  <si>
+    <t>Matheus &amp; Andre</t>
+  </si>
+  <si>
+    <t>Andre</t>
+  </si>
+  <si>
+    <t>Bea &amp; Rafa</t>
+  </si>
+  <si>
+    <t>Sônia &amp; Denilson</t>
+  </si>
+  <si>
+    <t>Langa</t>
+  </si>
+  <si>
+    <t>Guga</t>
+  </si>
+  <si>
+    <t>Teixeira</t>
+  </si>
+  <si>
+    <t>Baron</t>
+  </si>
+  <si>
+    <t>Dare</t>
+  </si>
+  <si>
+    <t>Zubk</t>
+  </si>
+  <si>
+    <t>Nath</t>
+  </si>
+  <si>
+    <t>Tony</t>
+  </si>
+  <si>
+    <t>Fiel</t>
+  </si>
+  <si>
+    <t>Bauer</t>
+  </si>
+  <si>
+    <t>Zangalli pai</t>
+  </si>
+  <si>
+    <t>Freire</t>
+  </si>
+  <si>
+    <t>Pudeulko</t>
+  </si>
+  <si>
+    <t>Rudi</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Mel</t>
+  </si>
+  <si>
+    <t>luciano</t>
+  </si>
+  <si>
+    <t>tarik</t>
+  </si>
+  <si>
+    <t>Aleksander</t>
+  </si>
+  <si>
+    <t>Luisa</t>
+  </si>
+  <si>
+    <t>Murilo Ferreira</t>
+  </si>
+  <si>
+    <t>Melke</t>
+  </si>
+  <si>
+    <t>Kennao</t>
+  </si>
+  <si>
+    <t>Matheus Assis</t>
+  </si>
+  <si>
+    <t>Vina</t>
+  </si>
+  <si>
+    <t>Gabi</t>
+  </si>
+  <si>
+    <t>Melissa</t>
+  </si>
+  <si>
+    <t>Murilo Oyafuso</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>Rud</t>
+  </si>
+  <si>
+    <t>Romano</t>
+  </si>
+  <si>
+    <t>Cheury</t>
+  </si>
+  <si>
+    <t>Johann</t>
+  </si>
+  <si>
+    <t>Metusalem</t>
+  </si>
+  <si>
+    <t>Berka</t>
+  </si>
+  <si>
+    <t>Arthur Castanhari</t>
+  </si>
+  <si>
+    <t>Carlos Kit</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Luís Zangalli</t>
+  </si>
+  <si>
+    <t>Ewerson</t>
+  </si>
+  <si>
+    <t>Gustavo dias</t>
+  </si>
+  <si>
+    <t>Gustavo taverna</t>
+  </si>
+  <si>
+    <t>Furiatti</t>
+  </si>
+  <si>
+    <t>Nakamura</t>
+  </si>
+  <si>
+    <t>Fabi</t>
+  </si>
+  <si>
+    <t>João Marmentini</t>
+  </si>
+  <si>
+    <t>Arthur</t>
+  </si>
+  <si>
+    <t>Ruanito</t>
+  </si>
+  <si>
+    <t>Zangalli  &amp; Clausius</t>
+  </si>
+  <si>
+    <t>Clausius</t>
+  </si>
+  <si>
+    <t>Du</t>
+  </si>
+  <si>
+    <t>Coelho</t>
+  </si>
+  <si>
+    <t>Nathalia</t>
+  </si>
+  <si>
+    <t>Lily</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>Hermann</t>
+  </si>
+  <si>
+    <t>Pietro</t>
+  </si>
+  <si>
+    <t>Luiz Henrique</t>
+  </si>
+  <si>
+    <t>liga-2x2-presencial-s3-e01</t>
+  </si>
+  <si>
+    <t>The Hosts of Mordor</t>
+  </si>
+  <si>
+    <t>Silverquill Statement</t>
+  </si>
+  <si>
+    <t>Chueiry &amp; Zangas</t>
+  </si>
+  <si>
+    <t>Chueiry &amp; Quintana</t>
+  </si>
+  <si>
+    <t>Chueiry &amp; Oscar</t>
+  </si>
+  <si>
+    <t>Arm for Battle</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F214"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1288,13 +1525,11 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="str">
-        <f>TRIM(LEFT(B2,FIND("&amp;",B2)-1))</f>
-        <v>Nobru</v>
-      </c>
-      <c r="D2" t="str">
-        <f>TRIM(RIGHT(B2,LEN(B2)-FIND("&amp;",B2)))</f>
-        <v>Metusa</v>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" t="s">
+        <v>167</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1310,13 +1545,11 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="str">
-        <f t="shared" ref="C3:C66" si="0">TRIM(LEFT(B3,FIND("&amp;",B3)-1))</f>
-        <v>Langa</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" ref="D3:D11" si="1">TRIM(RIGHT(B3,LEN(B3)-FIND("&amp;",B3)))</f>
-        <v>Guga</v>
+      <c r="C3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" t="s">
+        <v>312</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -1332,13 +1565,11 @@
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>Teixeira</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" si="1"/>
-        <v>Pedro</v>
+      <c r="C4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" t="s">
+        <v>206</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -1354,13 +1585,11 @@
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>Martin</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>Jorel</v>
+      <c r="C5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" t="s">
+        <v>158</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -1376,13 +1605,11 @@
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>Baron</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="1"/>
-        <v>Dare</v>
+      <c r="C6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D6" t="s">
+        <v>315</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -1398,13 +1625,11 @@
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>Zubk</v>
-      </c>
-      <c r="D7" t="str">
-        <f t="shared" si="1"/>
-        <v>Nath</v>
+      <c r="C7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>317</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -1420,13 +1645,11 @@
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>Nobru</v>
-      </c>
-      <c r="D8" t="str">
-        <f t="shared" si="1"/>
-        <v>Metusa</v>
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" t="s">
+        <v>167</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -1442,13 +1665,11 @@
       <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="str">
-        <f t="shared" si="0"/>
-        <v>Tony</v>
-      </c>
-      <c r="D9" t="str">
-        <f t="shared" si="1"/>
-        <v>Oscar</v>
+      <c r="C9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" t="s">
+        <v>230</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -1464,13 +1685,11 @@
       <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="str">
-        <f t="shared" si="0"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D10" t="str">
-        <f t="shared" si="1"/>
-        <v>Martin</v>
+      <c r="C10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" t="s">
+        <v>217</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -1486,13 +1705,11 @@
       <c r="B11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="str">
-        <f t="shared" si="0"/>
-        <v>Fiel</v>
-      </c>
-      <c r="D11" t="str">
-        <f t="shared" si="1"/>
-        <v>Werneck</v>
+      <c r="C11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" t="s">
+        <v>246</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -1508,13 +1725,11 @@
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="str">
-        <f t="shared" si="0"/>
-        <v>Bauer</v>
-      </c>
-      <c r="D12" t="str">
-        <f t="shared" ref="D12:D31" si="2">TRIM(RIGHT(B12,LEN(B12)-FIND("&amp;",B12)))</f>
-        <v>Langa</v>
+      <c r="C12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D12" t="s">
+        <v>311</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -1530,13 +1745,11 @@
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="str">
-        <f t="shared" si="0"/>
-        <v>Rudzzt</v>
-      </c>
-      <c r="D13" t="str">
-        <f t="shared" si="2"/>
-        <v>Metusa</v>
+      <c r="C13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" t="s">
+        <v>167</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -1552,13 +1765,11 @@
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="str">
-        <f t="shared" si="0"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D14" t="str">
-        <f t="shared" si="2"/>
-        <v>Martin</v>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" t="s">
+        <v>217</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -1574,13 +1785,11 @@
       <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="str">
-        <f t="shared" si="0"/>
-        <v>Zangalli</v>
-      </c>
-      <c r="D15" t="str">
-        <f t="shared" si="2"/>
-        <v>Zangalli pai</v>
+      <c r="C15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" t="s">
+        <v>321</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -1596,13 +1805,11 @@
       <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" t="str">
-        <f t="shared" si="0"/>
-        <v>Freire</v>
-      </c>
-      <c r="D16" t="str">
-        <f t="shared" si="2"/>
-        <v>Pudeulko</v>
+      <c r="C16" t="s">
+        <v>322</v>
+      </c>
+      <c r="D16" t="s">
+        <v>323</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
@@ -1618,13 +1825,11 @@
       <c r="B17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="str">
-        <f t="shared" si="0"/>
-        <v>Nobru</v>
-      </c>
-      <c r="D17" t="str">
-        <f t="shared" si="2"/>
-        <v>Tarik</v>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" t="s">
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
@@ -1640,13 +1845,11 @@
       <c r="B18" t="s">
         <v>42</v>
       </c>
-      <c r="C18" t="str">
-        <f t="shared" si="0"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D18" t="str">
-        <f t="shared" si="2"/>
-        <v>Rudi</v>
+      <c r="C18" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" t="s">
+        <v>324</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -1662,13 +1865,11 @@
       <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" t="str">
-        <f t="shared" si="0"/>
-        <v>Carlos</v>
-      </c>
-      <c r="D19" t="str">
-        <f t="shared" si="2"/>
-        <v>Mel</v>
+      <c r="C19" t="s">
+        <v>325</v>
+      </c>
+      <c r="D19" t="s">
+        <v>326</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -1684,13 +1885,11 @@
       <c r="B20" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="str">
-        <f t="shared" si="0"/>
-        <v>Matheus</v>
-      </c>
-      <c r="D20" t="str">
-        <f t="shared" si="2"/>
-        <v>luciano</v>
+      <c r="C20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" t="s">
+        <v>327</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -1726,13 +1925,11 @@
       <c r="B22" t="s">
         <v>45</v>
       </c>
-      <c r="C22" t="str">
-        <f t="shared" si="0"/>
-        <v>Nobru</v>
-      </c>
-      <c r="D22" t="str">
-        <f t="shared" si="2"/>
-        <v>tarik</v>
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" t="s">
+        <v>328</v>
       </c>
       <c r="E22" t="s">
         <v>48</v>
@@ -1748,13 +1945,11 @@
       <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="C23" t="str">
-        <f t="shared" si="0"/>
-        <v>Aleksander</v>
-      </c>
-      <c r="D23" t="str">
-        <f t="shared" si="2"/>
-        <v>Luisa</v>
+      <c r="C23" t="s">
+        <v>329</v>
+      </c>
+      <c r="D23" t="s">
+        <v>330</v>
       </c>
       <c r="E23" t="s">
         <v>40</v>
@@ -1770,13 +1965,11 @@
       <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="str">
-        <f t="shared" si="0"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D24" t="str">
-        <f t="shared" si="2"/>
-        <v>Martin</v>
+      <c r="C24" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" t="s">
+        <v>217</v>
       </c>
       <c r="E24" t="s">
         <v>48</v>
@@ -1792,13 +1985,11 @@
       <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="C25" t="str">
-        <f t="shared" si="0"/>
-        <v>Langa</v>
-      </c>
-      <c r="D25" t="str">
-        <f t="shared" si="2"/>
-        <v>Murilo Ferreira</v>
+      <c r="C25" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" t="s">
+        <v>331</v>
       </c>
       <c r="E25" t="s">
         <v>48</v>
@@ -1814,13 +2005,11 @@
       <c r="B26" t="s">
         <v>35</v>
       </c>
-      <c r="C26" t="str">
-        <f t="shared" si="0"/>
-        <v>Rudzzt</v>
-      </c>
-      <c r="D26" t="str">
-        <f t="shared" si="2"/>
-        <v>Metusa</v>
+      <c r="C26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" t="s">
+        <v>167</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -1836,13 +2025,11 @@
       <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" t="str">
-        <f t="shared" si="0"/>
-        <v>Melke</v>
-      </c>
-      <c r="D27" t="str">
-        <f t="shared" si="2"/>
-        <v>Gustavo Dias</v>
+      <c r="C27" t="s">
+        <v>332</v>
+      </c>
+      <c r="D27" t="s">
+        <v>300</v>
       </c>
       <c r="E27" t="s">
         <v>30</v>
@@ -1858,13 +2045,11 @@
       <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>Bauer</v>
-      </c>
-      <c r="D28" t="str">
-        <f t="shared" si="2"/>
-        <v>Kennao</v>
+      <c r="C28" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" t="s">
+        <v>333</v>
       </c>
       <c r="E28" t="s">
         <v>57</v>
@@ -1880,13 +2065,11 @@
       <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C29" t="str">
-        <f t="shared" si="0"/>
-        <v>Theo</v>
-      </c>
-      <c r="D29" t="str">
-        <f t="shared" si="2"/>
-        <v>Leonardo</v>
+      <c r="C29" t="s">
+        <v>223</v>
+      </c>
+      <c r="D29" t="s">
+        <v>224</v>
       </c>
       <c r="E29" t="s">
         <v>48</v>
@@ -1902,13 +2085,11 @@
       <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="C30" t="str">
-        <f t="shared" si="0"/>
-        <v>Matheus Assis</v>
-      </c>
-      <c r="D30" t="str">
-        <f t="shared" si="2"/>
-        <v>Luciano</v>
+      <c r="C30" t="s">
+        <v>334</v>
+      </c>
+      <c r="D30" t="s">
+        <v>194</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -1924,13 +2105,11 @@
       <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>Nobru</v>
-      </c>
-      <c r="D31" t="str">
-        <f t="shared" si="2"/>
-        <v>Nicolas</v>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" t="s">
+        <v>280</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -1946,13 +2125,11 @@
       <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="C32" t="str">
-        <f t="shared" si="0"/>
-        <v>Zangalli</v>
-      </c>
-      <c r="D32" t="str">
-        <f t="shared" ref="D32:D39" si="3">TRIM(RIGHT(B32,LEN(B32)-FIND("&amp;",B32)))</f>
-        <v>Vina</v>
+      <c r="C32" t="s">
+        <v>238</v>
+      </c>
+      <c r="D32" t="s">
+        <v>335</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -1968,13 +2145,11 @@
       <c r="B33" t="s">
         <v>10</v>
       </c>
-      <c r="C33" t="str">
-        <f t="shared" si="0"/>
-        <v>Martin</v>
-      </c>
-      <c r="D33" t="str">
-        <f t="shared" si="3"/>
-        <v>Jorel</v>
+      <c r="C33" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" t="s">
+        <v>158</v>
       </c>
       <c r="E33" t="s">
         <v>48</v>
@@ -1990,13 +2165,11 @@
       <c r="B34" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="str">
-        <f t="shared" si="0"/>
-        <v>Rudzzt</v>
-      </c>
-      <c r="D34" t="str">
-        <f t="shared" si="3"/>
-        <v>Metusa</v>
+      <c r="C34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" t="s">
+        <v>167</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -2012,13 +2185,11 @@
       <c r="B35" t="s">
         <v>62</v>
       </c>
-      <c r="C35" t="str">
-        <f t="shared" si="0"/>
-        <v>Melke</v>
-      </c>
-      <c r="D35" t="str">
-        <f t="shared" si="3"/>
-        <v>Sônia</v>
+      <c r="C35" t="s">
+        <v>332</v>
+      </c>
+      <c r="D35" t="s">
+        <v>197</v>
       </c>
       <c r="E35" t="s">
         <v>68</v>
@@ -2034,13 +2205,11 @@
       <c r="B36" t="s">
         <v>63</v>
       </c>
-      <c r="C36" t="str">
-        <f t="shared" si="0"/>
-        <v>Banshee</v>
-      </c>
-      <c r="D36" t="str">
-        <f t="shared" si="3"/>
-        <v>Gabi</v>
+      <c r="C36" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" t="s">
+        <v>336</v>
       </c>
       <c r="E36" t="s">
         <v>69</v>
@@ -2056,13 +2225,11 @@
       <c r="B37" t="s">
         <v>64</v>
       </c>
-      <c r="C37" t="str">
-        <f t="shared" si="0"/>
-        <v>Matheus</v>
-      </c>
-      <c r="D37" t="str">
-        <f t="shared" si="3"/>
-        <v>Murilo</v>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>228</v>
       </c>
       <c r="E37" t="s">
         <v>48</v>
@@ -2078,13 +2245,11 @@
       <c r="B38" t="s">
         <v>65</v>
       </c>
-      <c r="C38" t="str">
-        <f t="shared" si="0"/>
-        <v>Nobru</v>
-      </c>
-      <c r="D38" t="str">
-        <f t="shared" si="3"/>
-        <v>Guga</v>
+      <c r="C38" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" t="s">
+        <v>312</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -2100,13 +2265,11 @@
       <c r="B39" t="s">
         <v>66</v>
       </c>
-      <c r="C39" t="str">
-        <f t="shared" si="0"/>
-        <v>Manfrinato</v>
-      </c>
-      <c r="D39" t="str">
-        <f t="shared" si="3"/>
-        <v>Melissa</v>
+      <c r="C39" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" t="s">
+        <v>337</v>
       </c>
       <c r="E39" t="s">
         <v>70</v>
@@ -2122,16 +2285,14 @@
       <c r="B40" t="s">
         <v>72</v>
       </c>
-      <c r="C40" t="str">
-        <f t="shared" si="0"/>
-        <v>Murilo Oyafuso</v>
-      </c>
-      <c r="D40" t="str">
-        <f t="shared" ref="D40:D44" si="4">TRIM(RIGHT(B40,LEN(B40)-FIND("&amp;",B40)))</f>
-        <v>Castanhari</v>
+      <c r="C40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" t="s">
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="F40" t="s">
         <v>48</v>
@@ -2144,13 +2305,11 @@
       <c r="B41" t="s">
         <v>10</v>
       </c>
-      <c r="C41" t="str">
-        <f t="shared" si="0"/>
-        <v>Martin</v>
-      </c>
-      <c r="D41" t="str">
-        <f t="shared" si="4"/>
-        <v>Jorel</v>
+      <c r="C41" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" t="s">
+        <v>158</v>
       </c>
       <c r="E41" t="s">
         <v>48</v>
@@ -2166,19 +2325,17 @@
       <c r="B42" t="s">
         <v>73</v>
       </c>
-      <c r="C42" t="str">
-        <f t="shared" si="0"/>
-        <v>Oscar</v>
-      </c>
-      <c r="D42" t="str">
-        <f t="shared" si="4"/>
-        <v>Anthony</v>
+      <c r="C42" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" t="s">
+        <v>339</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2188,19 +2345,17 @@
       <c r="B43" t="s">
         <v>74</v>
       </c>
-      <c r="C43" t="str">
-        <f t="shared" si="0"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D43" t="str">
-        <f t="shared" si="4"/>
-        <v>Rud</v>
+      <c r="C43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" t="s">
+        <v>340</v>
       </c>
       <c r="E43" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" t="s">
         <v>77</v>
-      </c>
-      <c r="F43" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,13 +2365,11 @@
       <c r="B44" t="s">
         <v>75</v>
       </c>
-      <c r="C44" t="str">
-        <f t="shared" si="0"/>
-        <v>Matheus</v>
-      </c>
-      <c r="D44" t="str">
-        <f t="shared" si="4"/>
-        <v>Romano</v>
+      <c r="C44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" t="s">
+        <v>341</v>
       </c>
       <c r="E44" t="s">
         <v>40</v>
@@ -2227,18 +2380,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
         <v>25</v>
       </c>
-      <c r="C45" t="str">
-        <f t="shared" si="0"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D45" t="str">
-        <f t="shared" ref="D45:D52" si="5">TRIM(RIGHT(B45,LEN(B45)-FIND("&amp;",B45)))</f>
-        <v>Martin</v>
+      <c r="C45" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" t="s">
+        <v>217</v>
       </c>
       <c r="E45" t="s">
         <v>48</v>
@@ -2249,18 +2400,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" t="s">
         <v>79</v>
       </c>
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" si="0"/>
-        <v>Melk</v>
-      </c>
-      <c r="D46" t="str">
-        <f t="shared" si="5"/>
-        <v>Sônia</v>
+      <c r="C46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" t="s">
+        <v>197</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -2271,21 +2420,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" t="str">
-        <f t="shared" si="0"/>
-        <v>Zangalli</v>
-      </c>
-      <c r="D47" t="str">
-        <f t="shared" si="5"/>
-        <v>Cheury</v>
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" t="s">
+        <v>342</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F47" t="s">
         <v>31</v>
@@ -2293,18 +2440,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" t="str">
-        <f t="shared" si="0"/>
-        <v>Matheus</v>
-      </c>
-      <c r="D48" t="str">
-        <f t="shared" si="5"/>
-        <v>Johann</v>
+        <v>81</v>
+      </c>
+      <c r="C48" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" t="s">
+        <v>343</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2315,21 +2460,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" t="str">
-        <f t="shared" si="0"/>
-        <v>Metusalem</v>
-      </c>
-      <c r="D49" t="str">
-        <f t="shared" si="5"/>
-        <v>Ruddzt</v>
+        <v>82</v>
+      </c>
+      <c r="C49" t="s">
+        <v>344</v>
+      </c>
+      <c r="D49" t="s">
+        <v>219</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
@@ -2337,18 +2480,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" t="str">
-        <f t="shared" si="0"/>
-        <v>Oscar</v>
-      </c>
-      <c r="D50" t="str">
-        <f t="shared" si="5"/>
-        <v>Vini</v>
+        <v>83</v>
+      </c>
+      <c r="C50" t="s">
+        <v>230</v>
+      </c>
+      <c r="D50" t="s">
+        <v>231</v>
       </c>
       <c r="E50" t="s">
         <v>39</v>
@@ -2359,18 +2500,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" t="str">
-        <f t="shared" si="0"/>
-        <v>Berka</v>
-      </c>
-      <c r="D51" t="str">
-        <f t="shared" si="5"/>
-        <v>Nobru</v>
+        <v>84</v>
+      </c>
+      <c r="C51" t="s">
+        <v>345</v>
+      </c>
+      <c r="D51" t="s">
+        <v>170</v>
       </c>
       <c r="E51" t="s">
         <v>32</v>
@@ -2381,43 +2520,39 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C52" t="str">
-        <f t="shared" si="0"/>
-        <v>Theo</v>
-      </c>
-      <c r="D52" t="str">
-        <f t="shared" si="5"/>
-        <v>André</v>
+        <v>85</v>
+      </c>
+      <c r="C52" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" t="s">
+        <v>164</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="str">
-        <f t="shared" si="0"/>
-        <v>Metusalem</v>
-      </c>
-      <c r="D53" t="str">
-        <f t="shared" ref="D53:D61" si="6">TRIM(RIGHT(B53,LEN(B53)-FIND("&amp;",B53)))</f>
-        <v>Ruddzt</v>
+        <v>82</v>
+      </c>
+      <c r="C53" t="s">
+        <v>344</v>
+      </c>
+      <c r="D53" t="s">
+        <v>219</v>
       </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
@@ -2425,43 +2560,39 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" t="str">
-        <f t="shared" si="0"/>
-        <v>Murilo Oyafuso</v>
-      </c>
-      <c r="D54" t="str">
-        <f t="shared" si="6"/>
-        <v>Arthur Castanhari</v>
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>338</v>
+      </c>
+      <c r="D54" t="s">
+        <v>346</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
       </c>
       <c r="F54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" t="str">
-        <f t="shared" si="0"/>
-        <v>Carlos Kit</v>
-      </c>
-      <c r="D55" t="str">
-        <f t="shared" si="6"/>
-        <v>Gustavo Dias</v>
+        <v>89</v>
+      </c>
+      <c r="C55" t="s">
+        <v>347</v>
+      </c>
+      <c r="D55" t="s">
+        <v>300</v>
       </c>
       <c r="E55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F55" t="s">
         <v>39</v>
@@ -2469,18 +2600,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B56" t="s">
         <v>25</v>
       </c>
-      <c r="C56" t="str">
-        <f t="shared" si="0"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D56" t="str">
-        <f t="shared" si="6"/>
-        <v>Martin</v>
+      <c r="C56" t="s">
+        <v>158</v>
+      </c>
+      <c r="D56" t="s">
+        <v>217</v>
       </c>
       <c r="E56" t="s">
         <v>48</v>
@@ -2491,18 +2620,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" t="str">
-        <f t="shared" si="0"/>
-        <v>Nobru</v>
-      </c>
-      <c r="D57" t="str">
-        <f t="shared" si="6"/>
-        <v>Melk</v>
+        <v>90</v>
+      </c>
+      <c r="C57" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" t="s">
+        <v>165</v>
       </c>
       <c r="E57" t="s">
         <v>21</v>
@@ -2513,18 +2640,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" t="str">
-        <f t="shared" si="0"/>
-        <v>Eduardo</v>
-      </c>
-      <c r="D58" t="str">
-        <f t="shared" si="6"/>
-        <v>Luís Zangalli</v>
+        <v>91</v>
+      </c>
+      <c r="C58" t="s">
+        <v>348</v>
+      </c>
+      <c r="D58" t="s">
+        <v>349</v>
       </c>
       <c r="E58" t="s">
         <v>40</v>
@@ -2535,18 +2660,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="str">
-        <f t="shared" si="0"/>
-        <v>Ewerson</v>
-      </c>
-      <c r="D59" t="str">
-        <f t="shared" si="6"/>
-        <v>Gabriel</v>
+        <v>92</v>
+      </c>
+      <c r="C59" t="s">
+        <v>350</v>
+      </c>
+      <c r="D59" t="s">
+        <v>242</v>
       </c>
       <c r="E59" t="s">
         <v>40</v>
@@ -2557,18 +2680,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" t="str">
-        <f t="shared" si="0"/>
-        <v>André</v>
-      </c>
-      <c r="D60" t="str">
-        <f t="shared" si="6"/>
-        <v>Matheus</v>
+        <v>93</v>
+      </c>
+      <c r="C60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D60" t="s">
+        <v>191</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
@@ -2579,18 +2700,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="str">
-        <f t="shared" si="0"/>
-        <v>Oscar</v>
-      </c>
-      <c r="D61" t="str">
-        <f t="shared" si="6"/>
-        <v>Vini</v>
+        <v>83</v>
+      </c>
+      <c r="C61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" t="s">
+        <v>231</v>
       </c>
       <c r="E61" t="s">
         <v>39</v>
@@ -2601,21 +2720,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62" t="s">
+        <v>166</v>
+      </c>
+      <c r="D62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E62" t="s">
         <v>105</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" t="str">
-        <f t="shared" si="0"/>
-        <v>Sonia</v>
-      </c>
-      <c r="D62" t="str">
-        <f t="shared" ref="D62:D69" si="7">TRIM(RIGHT(B62,LEN(B62)-FIND("&amp;",B62)))</f>
-        <v>Melk</v>
-      </c>
-      <c r="E62" t="s">
-        <v>106</v>
       </c>
       <c r="F62" t="s">
         <v>17</v>
@@ -2623,18 +2740,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
-      </c>
-      <c r="C63" t="str">
-        <f t="shared" si="0"/>
-        <v>Gustavo dias</v>
-      </c>
-      <c r="D63" t="str">
-        <f t="shared" si="7"/>
-        <v>Gustavo taverna</v>
+        <v>98</v>
+      </c>
+      <c r="C63" t="s">
+        <v>351</v>
+      </c>
+      <c r="D63" t="s">
+        <v>352</v>
       </c>
       <c r="E63" t="s">
         <v>40</v>
@@ -2645,40 +2760,36 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" t="str">
-        <f t="shared" si="0"/>
-        <v>Martin</v>
-      </c>
-      <c r="D64" t="str">
-        <f t="shared" si="7"/>
-        <v>Banshee</v>
+        <v>99</v>
+      </c>
+      <c r="C64" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" t="s">
+        <v>159</v>
       </c>
       <c r="E64" t="s">
+        <v>106</v>
+      </c>
+      <c r="F64" t="s">
         <v>107</v>
-      </c>
-      <c r="F64" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
-      </c>
-      <c r="C65" t="str">
-        <f t="shared" si="0"/>
-        <v>Furiatti</v>
-      </c>
-      <c r="D65" t="str">
-        <f t="shared" si="7"/>
-        <v>Nakamura</v>
+        <v>100</v>
+      </c>
+      <c r="C65" t="s">
+        <v>353</v>
+      </c>
+      <c r="D65" t="s">
+        <v>354</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -2689,18 +2800,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" t="str">
-        <f t="shared" si="0"/>
-        <v>Fabi</v>
-      </c>
-      <c r="D66" t="str">
-        <f t="shared" si="7"/>
-        <v>João Marmentini</v>
+        <v>101</v>
+      </c>
+      <c r="C66" t="s">
+        <v>355</v>
+      </c>
+      <c r="D66" t="s">
+        <v>356</v>
       </c>
       <c r="E66" t="s">
         <v>13</v>
@@ -2711,40 +2820,36 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" t="str">
-        <f t="shared" ref="C67:C113" si="8">TRIM(LEFT(B67,FIND("&amp;",B67)-1))</f>
-        <v>Metusa</v>
-      </c>
-      <c r="D67" t="str">
-        <f t="shared" si="7"/>
-        <v>Ruddzt</v>
+        <v>102</v>
+      </c>
+      <c r="C67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" t="s">
+        <v>219</v>
       </c>
       <c r="E67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
-      </c>
-      <c r="C68" t="str">
-        <f t="shared" si="8"/>
-        <v>Oscar</v>
-      </c>
-      <c r="D68" t="str">
-        <f t="shared" si="7"/>
-        <v>Vini</v>
+        <v>83</v>
+      </c>
+      <c r="C68" t="s">
+        <v>230</v>
+      </c>
+      <c r="D68" t="s">
+        <v>231</v>
       </c>
       <c r="E68" t="s">
         <v>31</v>
@@ -2755,65 +2860,59 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" t="str">
-        <f t="shared" si="8"/>
-        <v>Romano</v>
-      </c>
-      <c r="D69" t="str">
-        <f t="shared" si="7"/>
-        <v>Matheus</v>
+        <v>103</v>
+      </c>
+      <c r="C69" t="s">
+        <v>341</v>
+      </c>
+      <c r="D69" t="s">
+        <v>191</v>
       </c>
       <c r="E69" t="s">
+        <v>108</v>
+      </c>
+      <c r="F69" t="s">
         <v>109</v>
-      </c>
-      <c r="F69" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>113</v>
+      </c>
+      <c r="B70" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" t="s">
         <v>114</v>
       </c>
-      <c r="B70" t="s">
-        <v>111</v>
-      </c>
-      <c r="C70" t="str">
-        <f t="shared" si="8"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D70" t="str">
-        <f t="shared" ref="D70:D75" si="9">TRIM(RIGHT(B70,LEN(B70)-FIND("&amp;",B70)))</f>
-        <v>Banshee</v>
-      </c>
-      <c r="E70" t="s">
-        <v>115</v>
-      </c>
       <c r="F70" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
-      </c>
-      <c r="C71" t="str">
-        <f t="shared" si="8"/>
-        <v>Melk</v>
-      </c>
-      <c r="D71" t="str">
-        <f t="shared" si="9"/>
-        <v>Sonia</v>
+        <v>111</v>
+      </c>
+      <c r="C71" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71" t="s">
+        <v>166</v>
       </c>
       <c r="E71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F71" t="s">
         <v>17</v>
@@ -2821,40 +2920,36 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
-      </c>
-      <c r="C72" t="str">
-        <f t="shared" si="8"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D72" t="str">
-        <f t="shared" si="9"/>
-        <v>Ruddzt</v>
+        <v>102</v>
+      </c>
+      <c r="C72" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" t="s">
+        <v>219</v>
       </c>
       <c r="E72" t="s">
+        <v>116</v>
+      </c>
+      <c r="F72" t="s">
         <v>117</v>
-      </c>
-      <c r="F72" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
-      </c>
-      <c r="C73" t="str">
-        <f t="shared" si="8"/>
-        <v>Matheus</v>
-      </c>
-      <c r="D73" t="str">
-        <f t="shared" si="9"/>
-        <v>Beck</v>
+        <v>112</v>
+      </c>
+      <c r="C73" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" t="s">
+        <v>184</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -2865,21 +2960,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" t="s">
+        <v>230</v>
+      </c>
+      <c r="D74" t="s">
+        <v>231</v>
+      </c>
+      <c r="E74" t="s">
         <v>114</v>
-      </c>
-      <c r="B74" t="s">
-        <v>84</v>
-      </c>
-      <c r="C74" t="str">
-        <f t="shared" si="8"/>
-        <v>Oscar</v>
-      </c>
-      <c r="D74" t="str">
-        <f t="shared" si="9"/>
-        <v>Vini</v>
-      </c>
-      <c r="E74" t="s">
-        <v>115</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
@@ -2887,65 +2980,59 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" t="str">
-        <f t="shared" si="8"/>
-        <v>Murilo Oyafuso</v>
-      </c>
-      <c r="D75" t="str">
-        <f t="shared" si="9"/>
-        <v>Arthur Castanhari</v>
+        <v>88</v>
+      </c>
+      <c r="C75" t="s">
+        <v>338</v>
+      </c>
+      <c r="D75" t="s">
+        <v>346</v>
       </c>
       <c r="E75" t="s">
+        <v>108</v>
+      </c>
+      <c r="F75" t="s">
         <v>109</v>
-      </c>
-      <c r="F75" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
       </c>
-      <c r="C76" t="str">
-        <f t="shared" si="8"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D76" t="str">
-        <f t="shared" ref="D76:D84" si="10">TRIM(RIGHT(B76,LEN(B76)-FIND("&amp;",B76)))</f>
-        <v>Martin</v>
+      <c r="C76" t="s">
+        <v>158</v>
+      </c>
+      <c r="D76" t="s">
+        <v>217</v>
       </c>
       <c r="E76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B77" t="s">
-        <v>119</v>
-      </c>
-      <c r="C77" t="str">
-        <f t="shared" si="8"/>
-        <v>Murilo</v>
-      </c>
-      <c r="D77" t="str">
-        <f t="shared" si="10"/>
-        <v>Arthur</v>
+        <v>118</v>
+      </c>
+      <c r="C77" t="s">
+        <v>228</v>
+      </c>
+      <c r="D77" t="s">
+        <v>357</v>
       </c>
       <c r="E77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F77" t="s">
         <v>48</v>
@@ -2953,21 +3040,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
-      </c>
-      <c r="C78" t="str">
-        <f t="shared" si="8"/>
-        <v>Banshee</v>
-      </c>
-      <c r="D78" t="str">
-        <f t="shared" si="10"/>
-        <v>Ruanito</v>
+        <v>119</v>
+      </c>
+      <c r="C78" t="s">
+        <v>159</v>
+      </c>
+      <c r="D78" t="s">
+        <v>358</v>
       </c>
       <c r="E78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F78" t="s">
         <v>48</v>
@@ -2975,21 +3060,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B79" t="s">
-        <v>103</v>
-      </c>
-      <c r="C79" t="str">
-        <f t="shared" si="8"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D79" t="str">
-        <f t="shared" si="10"/>
-        <v>Ruddzt</v>
+        <v>102</v>
+      </c>
+      <c r="C79" t="s">
+        <v>167</v>
+      </c>
+      <c r="D79" t="s">
+        <v>219</v>
       </c>
       <c r="E79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F79" t="s">
         <v>30</v>
@@ -2997,21 +3080,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>121</v>
-      </c>
-      <c r="C80" t="str">
-        <f t="shared" si="8"/>
-        <v>Beck</v>
-      </c>
-      <c r="D80" t="str">
-        <f t="shared" si="10"/>
-        <v>Gus</v>
+        <v>120</v>
+      </c>
+      <c r="C80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" t="s">
+        <v>299</v>
       </c>
       <c r="E80" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F80" t="s">
         <v>15</v>
@@ -3019,18 +3100,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
-      </c>
-      <c r="C81" t="str">
-        <f t="shared" si="8"/>
-        <v>Melk</v>
-      </c>
-      <c r="D81" t="str">
-        <f t="shared" si="10"/>
-        <v>Sonia</v>
+        <v>111</v>
+      </c>
+      <c r="C81" t="s">
+        <v>165</v>
+      </c>
+      <c r="D81" t="s">
+        <v>166</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -3041,109 +3120,99 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
-      </c>
-      <c r="C82" t="str">
-        <f t="shared" si="8"/>
-        <v>Rogério</v>
-      </c>
-      <c r="D82" t="str">
-        <f t="shared" si="10"/>
-        <v>Nathan</v>
+        <v>121</v>
+      </c>
+      <c r="C82" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" t="s">
+        <v>222</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
       </c>
       <c r="F82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B83" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" t="str">
-        <f t="shared" si="8"/>
-        <v>Zangalli</v>
-      </c>
-      <c r="D83" t="str">
-        <f t="shared" si="10"/>
-        <v>Clausius</v>
+        <v>359</v>
+      </c>
+      <c r="C83" t="s">
+        <v>238</v>
+      </c>
+      <c r="D83" t="s">
+        <v>360</v>
       </c>
       <c r="E83" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>122</v>
+      </c>
+      <c r="B84" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" t="s">
+        <v>164</v>
+      </c>
+      <c r="D84" t="s">
+        <v>191</v>
+      </c>
+      <c r="E84" t="s">
+        <v>108</v>
+      </c>
+      <c r="F84" t="s">
         <v>124</v>
-      </c>
-      <c r="B84" t="s">
-        <v>94</v>
-      </c>
-      <c r="C84" t="str">
-        <f t="shared" si="8"/>
-        <v>André</v>
-      </c>
-      <c r="D84" t="str">
-        <f t="shared" si="10"/>
-        <v>Matheus</v>
-      </c>
-      <c r="E84" t="s">
-        <v>109</v>
-      </c>
-      <c r="F84" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B85" t="s">
-        <v>127</v>
-      </c>
-      <c r="C85" t="str">
-        <f t="shared" si="8"/>
-        <v>Arthur</v>
-      </c>
-      <c r="D85" t="str">
-        <f t="shared" ref="D85:D91" si="11">TRIM(RIGHT(B85,LEN(B85)-FIND("&amp;",B85)))</f>
-        <v>Oyafuso</v>
+        <v>125</v>
+      </c>
+      <c r="C85" t="s">
+        <v>357</v>
+      </c>
+      <c r="D85" t="s">
+        <v>178</v>
       </c>
       <c r="E85" t="s">
         <v>30</v>
       </c>
       <c r="F85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" t="str">
-        <f t="shared" si="8"/>
-        <v>Melk</v>
-      </c>
-      <c r="D86" t="str">
-        <f t="shared" si="11"/>
-        <v>Sônia</v>
+        <v>79</v>
+      </c>
+      <c r="C86" t="s">
+        <v>165</v>
+      </c>
+      <c r="D86" t="s">
+        <v>197</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -3151,21 +3220,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
-      </c>
-      <c r="C87" t="str">
-        <f t="shared" si="8"/>
-        <v>Martin</v>
-      </c>
-      <c r="D87" t="str">
-        <f t="shared" si="11"/>
-        <v>Banshee</v>
+        <v>99</v>
+      </c>
+      <c r="C87" t="s">
+        <v>217</v>
+      </c>
+      <c r="D87" t="s">
+        <v>159</v>
       </c>
       <c r="E87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F87" t="s">
         <v>48</v>
@@ -3173,106 +3240,96 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B88" t="s">
-        <v>131</v>
-      </c>
-      <c r="C88" t="str">
-        <f t="shared" si="8"/>
-        <v>Andre</v>
-      </c>
-      <c r="D88" t="str">
-        <f t="shared" si="11"/>
-        <v>Matheus</v>
+        <v>129</v>
+      </c>
+      <c r="C88" t="s">
+        <v>308</v>
+      </c>
+      <c r="D88" t="s">
+        <v>191</v>
       </c>
       <c r="E88" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F88" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B89" t="s">
-        <v>132</v>
-      </c>
-      <c r="C89" t="str">
-        <f t="shared" si="8"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D89" t="str">
-        <f t="shared" si="11"/>
-        <v>Rudzzt</v>
+        <v>130</v>
+      </c>
+      <c r="C89" t="s">
+        <v>167</v>
+      </c>
+      <c r="D89" t="s">
+        <v>168</v>
       </c>
       <c r="E89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F89" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B90" t="s">
-        <v>133</v>
-      </c>
-      <c r="C90" t="str">
-        <f t="shared" si="8"/>
-        <v>Gustavo Dias</v>
-      </c>
-      <c r="D90" t="str">
-        <f t="shared" si="11"/>
-        <v>Luciano</v>
+        <v>131</v>
+      </c>
+      <c r="C90" t="s">
+        <v>300</v>
+      </c>
+      <c r="D90" t="s">
+        <v>194</v>
       </c>
       <c r="E90" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s">
-        <v>134</v>
-      </c>
-      <c r="C91" t="str">
-        <f t="shared" si="8"/>
-        <v>Berka</v>
-      </c>
-      <c r="D91" t="str">
-        <f t="shared" si="11"/>
-        <v>Du</v>
+        <v>132</v>
+      </c>
+      <c r="C91" t="s">
+        <v>345</v>
+      </c>
+      <c r="D91" t="s">
+        <v>361</v>
       </c>
       <c r="E91" t="s">
         <v>31</v>
       </c>
       <c r="F91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
-      </c>
-      <c r="C92" t="str">
-        <f t="shared" si="8"/>
-        <v>Nathan</v>
-      </c>
-      <c r="D92" t="str">
-        <f t="shared" ref="D92" si="12">TRIM(RIGHT(B92,LEN(B92)-FIND("&amp;",B92)))</f>
-        <v>Coelho</v>
+        <v>133</v>
+      </c>
+      <c r="C92" t="s">
+        <v>222</v>
+      </c>
+      <c r="D92" t="s">
+        <v>362</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -3283,43 +3340,39 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
         <v>25</v>
       </c>
-      <c r="C93" t="str">
-        <f t="shared" si="8"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D93" t="str">
-        <f t="shared" ref="D93:D105" si="13">TRIM(RIGHT(B93,LEN(B93)-FIND("&amp;",B93)))</f>
-        <v>Martin</v>
+      <c r="C93" t="s">
+        <v>158</v>
+      </c>
+      <c r="D93" t="s">
+        <v>217</v>
       </c>
       <c r="E93" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
-      </c>
-      <c r="C94" t="str">
-        <f t="shared" si="8"/>
-        <v>Melk</v>
-      </c>
-      <c r="D94" t="str">
-        <f t="shared" si="13"/>
-        <v>Sonia</v>
+        <v>111</v>
+      </c>
+      <c r="C94" t="s">
+        <v>165</v>
+      </c>
+      <c r="D94" t="s">
+        <v>166</v>
       </c>
       <c r="E94" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F94" t="s">
         <v>30</v>
@@ -3327,21 +3380,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B95" t="s">
-        <v>138</v>
-      </c>
-      <c r="C95" t="str">
-        <f t="shared" si="8"/>
-        <v>Lucas</v>
-      </c>
-      <c r="D95" t="str">
-        <f t="shared" si="13"/>
-        <v>Luiz Rodrigues</v>
+        <v>136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>284</v>
+      </c>
+      <c r="D95" t="s">
+        <v>181</v>
       </c>
       <c r="E95" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -3349,21 +3400,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" t="s">
         <v>137</v>
       </c>
-      <c r="B96" t="s">
-        <v>139</v>
-      </c>
-      <c r="C96" t="str">
-        <f t="shared" si="8"/>
-        <v>Nathalia</v>
-      </c>
-      <c r="D96" t="str">
-        <f t="shared" si="13"/>
-        <v>Lily</v>
+      <c r="C96" t="s">
+        <v>363</v>
+      </c>
+      <c r="D96" t="s">
+        <v>364</v>
       </c>
       <c r="E96" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F96" t="s">
         <v>59</v>
@@ -3371,84 +3420,76 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
-      </c>
-      <c r="C97" t="str">
-        <f t="shared" si="8"/>
-        <v>Zangalli</v>
-      </c>
-      <c r="D97" t="str">
-        <f t="shared" si="13"/>
-        <v>Banshee</v>
+        <v>138</v>
+      </c>
+      <c r="C97" t="s">
+        <v>238</v>
+      </c>
+      <c r="D97" t="s">
+        <v>159</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
-      </c>
-      <c r="C98" t="str">
-        <f t="shared" si="8"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D98" t="str">
-        <f t="shared" si="13"/>
-        <v>Rudzzt</v>
+        <v>130</v>
+      </c>
+      <c r="C98" t="s">
+        <v>167</v>
+      </c>
+      <c r="D98" t="s">
+        <v>168</v>
       </c>
       <c r="E98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F98" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
-      </c>
-      <c r="C99" t="str">
-        <f t="shared" si="8"/>
-        <v>Castanhari</v>
-      </c>
-      <c r="D99" t="str">
-        <f t="shared" si="13"/>
-        <v>Oyafuso</v>
+        <v>139</v>
+      </c>
+      <c r="C99" t="s">
+        <v>177</v>
+      </c>
+      <c r="D99" t="s">
+        <v>178</v>
       </c>
       <c r="E99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F99" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>142</v>
-      </c>
-      <c r="C100" t="str">
-        <f t="shared" si="8"/>
-        <v>Beck</v>
-      </c>
-      <c r="D100" t="str">
-        <f t="shared" si="13"/>
-        <v>Ricardo</v>
+        <v>140</v>
+      </c>
+      <c r="C100" t="s">
+        <v>184</v>
+      </c>
+      <c r="D100" t="s">
+        <v>365</v>
       </c>
       <c r="E100" t="s">
         <v>15</v>
@@ -3459,40 +3500,36 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
-        <v>143</v>
-      </c>
-      <c r="C101" t="str">
-        <f t="shared" si="8"/>
-        <v>Matheus</v>
-      </c>
-      <c r="D101" t="str">
-        <f t="shared" si="13"/>
-        <v>André</v>
+        <v>141</v>
+      </c>
+      <c r="C101" t="s">
+        <v>191</v>
+      </c>
+      <c r="D101" t="s">
+        <v>164</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
       </c>
       <c r="F101" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
-      </c>
-      <c r="C102" t="str">
-        <f t="shared" si="8"/>
-        <v>João</v>
-      </c>
-      <c r="D102" t="str">
-        <f t="shared" si="13"/>
-        <v>Hermann</v>
+        <v>142</v>
+      </c>
+      <c r="C102" t="s">
+        <v>209</v>
+      </c>
+      <c r="D102" t="s">
+        <v>366</v>
       </c>
       <c r="E102" t="s">
         <v>40</v>
@@ -3503,18 +3540,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
-      </c>
-      <c r="C103" t="str">
-        <f t="shared" si="8"/>
-        <v>Pietro</v>
-      </c>
-      <c r="D103" t="str">
-        <f t="shared" si="13"/>
-        <v>Luiz Henrique</v>
+        <v>143</v>
+      </c>
+      <c r="C103" t="s">
+        <v>367</v>
+      </c>
+      <c r="D103" t="s">
+        <v>368</v>
       </c>
       <c r="E103" t="s">
         <v>49</v>
@@ -3525,40 +3560,36 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
         <v>53</v>
       </c>
-      <c r="C104" t="str">
-        <f t="shared" si="8"/>
-        <v>Theo</v>
-      </c>
-      <c r="D104" t="str">
-        <f t="shared" si="13"/>
-        <v>Leonardo</v>
+      <c r="C104" t="s">
+        <v>223</v>
+      </c>
+      <c r="D104" t="s">
+        <v>224</v>
       </c>
       <c r="E104" t="s">
         <v>13</v>
       </c>
       <c r="F104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B105" t="s">
-        <v>146</v>
-      </c>
-      <c r="C105" t="str">
-        <f t="shared" si="8"/>
-        <v>Nathan</v>
-      </c>
-      <c r="D105" t="str">
-        <f t="shared" si="13"/>
-        <v>Rogério</v>
+        <v>144</v>
+      </c>
+      <c r="C105" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" t="s">
+        <v>269</v>
       </c>
       <c r="E105" t="s">
         <v>48</v>
@@ -3569,21 +3600,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
-      </c>
-      <c r="C106" t="str">
-        <f t="shared" si="8"/>
-        <v>Melk</v>
-      </c>
-      <c r="D106" t="str">
-        <f t="shared" ref="D106:D113" si="14">TRIM(RIGHT(B106,LEN(B106)-FIND("&amp;",B106)))</f>
-        <v>Sonia</v>
+        <v>111</v>
+      </c>
+      <c r="C106" t="s">
+        <v>165</v>
+      </c>
+      <c r="D106" t="s">
+        <v>166</v>
       </c>
       <c r="E106" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F106" t="s">
         <v>30</v>
@@ -3591,21 +3620,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
-      </c>
-      <c r="C107" t="str">
-        <f t="shared" si="8"/>
-        <v>Metusa</v>
-      </c>
-      <c r="D107" t="str">
-        <f t="shared" si="14"/>
-        <v>Rudzzt</v>
+        <v>130</v>
+      </c>
+      <c r="C107" t="s">
+        <v>167</v>
+      </c>
+      <c r="D107" t="s">
+        <v>168</v>
       </c>
       <c r="E107" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F107" t="s">
         <v>20</v>
@@ -3613,43 +3640,39 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B108" t="s">
-        <v>141</v>
-      </c>
-      <c r="C108" t="str">
-        <f t="shared" si="8"/>
-        <v>Castanhari</v>
-      </c>
-      <c r="D108" t="str">
-        <f t="shared" si="14"/>
-        <v>Oyafuso</v>
+        <v>139</v>
+      </c>
+      <c r="C108" t="s">
+        <v>177</v>
+      </c>
+      <c r="D108" t="s">
+        <v>178</v>
       </c>
       <c r="E108" t="s">
         <v>13</v>
       </c>
       <c r="F108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B109" t="s">
-        <v>151</v>
-      </c>
-      <c r="C109" t="str">
-        <f t="shared" si="8"/>
-        <v>Kit</v>
-      </c>
-      <c r="D109" t="str">
-        <f t="shared" si="14"/>
-        <v>Gustavo</v>
+        <v>149</v>
+      </c>
+      <c r="C109" t="s">
+        <v>171</v>
+      </c>
+      <c r="D109" t="s">
+        <v>275</v>
       </c>
       <c r="E109" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F109" t="s">
         <v>39</v>
@@ -3657,65 +3680,59 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B110" t="s">
         <v>25</v>
       </c>
-      <c r="C110" t="str">
-        <f t="shared" si="8"/>
-        <v>Jorel</v>
-      </c>
-      <c r="D110" t="str">
-        <f t="shared" si="14"/>
-        <v>Martin</v>
+      <c r="C110" t="s">
+        <v>158</v>
+      </c>
+      <c r="D110" t="s">
+        <v>217</v>
       </c>
       <c r="E110" t="s">
         <v>48</v>
       </c>
       <c r="F110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" t="s">
+        <v>150</v>
+      </c>
+      <c r="C111" t="s">
+        <v>343</v>
+      </c>
+      <c r="D111" t="s">
+        <v>191</v>
+      </c>
+      <c r="E111" t="s">
         <v>155</v>
       </c>
-      <c r="B111" t="s">
-        <v>152</v>
-      </c>
-      <c r="C111" t="str">
-        <f t="shared" si="8"/>
-        <v>Johann</v>
-      </c>
-      <c r="D111" t="str">
-        <f t="shared" si="14"/>
-        <v>Matheus</v>
-      </c>
-      <c r="E111" t="s">
-        <v>157</v>
-      </c>
       <c r="F111" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B112" t="s">
-        <v>153</v>
-      </c>
-      <c r="C112" t="str">
-        <f t="shared" si="8"/>
-        <v>André</v>
-      </c>
-      <c r="D112" t="str">
-        <f t="shared" si="14"/>
-        <v>Zangalli</v>
+        <v>151</v>
+      </c>
+      <c r="C112" t="s">
+        <v>164</v>
+      </c>
+      <c r="D112" t="s">
+        <v>238</v>
       </c>
       <c r="E112" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F112" t="s">
         <v>13</v>
@@ -3723,18 +3740,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B113" t="s">
-        <v>154</v>
-      </c>
-      <c r="C113" t="str">
-        <f t="shared" si="8"/>
-        <v>Rogério</v>
-      </c>
-      <c r="D113" t="str">
-        <f t="shared" si="14"/>
-        <v>Beck</v>
+        <v>152</v>
+      </c>
+      <c r="C113" t="s">
+        <v>269</v>
+      </c>
+      <c r="D113" t="s">
+        <v>184</v>
       </c>
       <c r="E113" t="s">
         <v>48</v>
@@ -3745,59 +3760,59 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>157</v>
+      </c>
+      <c r="B114" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" t="s">
+        <v>158</v>
+      </c>
+      <c r="D114" t="s">
         <v>159</v>
       </c>
-      <c r="B114" t="s">
-        <v>111</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
         <v>160</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
         <v>161</v>
-      </c>
-      <c r="E114" t="s">
-        <v>162</v>
-      </c>
-      <c r="F114" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B115" t="s">
+        <v>162</v>
+      </c>
+      <c r="C115" t="s">
+        <v>163</v>
+      </c>
+      <c r="D115" t="s">
         <v>164</v>
-      </c>
-      <c r="C115" t="s">
-        <v>165</v>
-      </c>
-      <c r="D115" t="s">
-        <v>166</v>
       </c>
       <c r="E115" t="s">
         <v>31</v>
       </c>
       <c r="F115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D116" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E116" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F116" t="s">
         <v>30</v>
@@ -3805,59 +3820,59 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D117" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E117" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F117" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B118" t="s">
+        <v>169</v>
+      </c>
+      <c r="C118" t="s">
+        <v>170</v>
+      </c>
+      <c r="D118" t="s">
         <v>171</v>
       </c>
-      <c r="C118" t="s">
+      <c r="E118" t="s">
+        <v>160</v>
+      </c>
+      <c r="F118" t="s">
         <v>172</v>
-      </c>
-      <c r="D118" t="s">
-        <v>173</v>
-      </c>
-      <c r="E118" t="s">
-        <v>162</v>
-      </c>
-      <c r="F118" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B119" t="s">
+        <v>173</v>
+      </c>
+      <c r="C119" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" t="s">
         <v>175</v>
       </c>
-      <c r="C119" t="s">
+      <c r="E119" t="s">
         <v>176</v>
-      </c>
-      <c r="D119" t="s">
-        <v>177</v>
-      </c>
-      <c r="E119" t="s">
-        <v>178</v>
       </c>
       <c r="F119" t="s">
         <v>14</v>
@@ -3865,99 +3880,99 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B120" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C120" t="s">
+        <v>177</v>
+      </c>
+      <c r="D120" t="s">
+        <v>178</v>
+      </c>
+      <c r="E120" t="s">
         <v>179</v>
       </c>
-      <c r="D120" t="s">
-        <v>180</v>
-      </c>
-      <c r="E120" t="s">
-        <v>181</v>
-      </c>
       <c r="F120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B121" t="s">
+        <v>180</v>
+      </c>
+      <c r="C121" t="s">
+        <v>181</v>
+      </c>
+      <c r="D121" t="s">
         <v>182</v>
       </c>
-      <c r="C121" t="s">
-        <v>183</v>
-      </c>
-      <c r="D121" t="s">
-        <v>184</v>
-      </c>
       <c r="E121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F121" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>185</v>
+        <v>369</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C122" t="s">
+        <v>158</v>
+      </c>
+      <c r="D122" t="s">
+        <v>159</v>
+      </c>
+      <c r="E122" t="s">
         <v>160</v>
       </c>
-      <c r="D122" t="s">
-        <v>161</v>
-      </c>
-      <c r="E122" t="s">
-        <v>162</v>
-      </c>
       <c r="F122" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>185</v>
+        <v>369</v>
       </c>
       <c r="B123" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C123" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D123" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E123" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F123" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>185</v>
+        <v>369</v>
       </c>
       <c r="B124" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D124" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E124" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F124" t="s">
         <v>15</v>
@@ -3965,36 +3980,36 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>185</v>
+        <v>369</v>
       </c>
       <c r="B125" t="s">
         <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D125" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E125" t="s">
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>185</v>
+        <v>369</v>
       </c>
       <c r="B126" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C126" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D126" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
@@ -4005,19 +4020,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B127" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C127" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D127" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E127" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F127" t="s">
         <v>15</v>
@@ -4025,19 +4040,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>190</v>
+      </c>
+      <c r="B128" t="s">
         <v>193</v>
       </c>
-      <c r="B128" t="s">
-        <v>196</v>
-      </c>
       <c r="C128" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D128" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E128" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F128" t="s">
         <v>60</v>
@@ -4045,19 +4060,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B129" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C129" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D129" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E129" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F129" t="s">
         <v>27</v>
@@ -4065,176 +4080,176 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B130" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C130" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D130" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E130" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F130" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B131" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C131" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D131" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B132" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C132" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D132" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E132" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F132" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B133" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C133" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D133" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E133" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F133" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B134" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C134" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D134" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E134" t="s">
         <v>29</v>
       </c>
       <c r="F134" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C135" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D135" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E135" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F135" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B136" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C136" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D136" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E136" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F136" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B137" t="s">
         <v>38</v>
       </c>
       <c r="C137" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D137" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B138" t="s">
         <v>25</v>
       </c>
       <c r="C138" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D138" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E138" t="s">
         <v>59</v>
@@ -4245,39 +4260,39 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B139" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C139" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E139" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F139" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B140" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C140" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D140" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E140" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F140" t="s">
         <v>17</v>
@@ -4285,39 +4300,39 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B141" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C141" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D141" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E141" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F141" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>216</v>
+      </c>
+      <c r="B142" t="s">
         <v>221</v>
       </c>
-      <c r="B142" t="s">
-        <v>226</v>
-      </c>
       <c r="C142" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D142" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E142" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F142" t="s">
         <v>60</v>
@@ -4325,39 +4340,39 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B143" t="s">
         <v>53</v>
       </c>
       <c r="C143" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D143" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E143" t="s">
         <v>48</v>
       </c>
       <c r="F143" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B144" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C144" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D144" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E144" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F144" t="s">
         <v>15</v>
@@ -4365,19 +4380,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B145" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C145" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D145" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E145" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F145" t="s">
         <v>27</v>
@@ -4385,16 +4400,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B146" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C146" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D146" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -4405,19 +4420,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B147" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C147" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D147" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E147" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F147" t="s">
         <v>21</v>
@@ -4425,119 +4440,119 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B148" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D148" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
       </c>
       <c r="F148" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C149" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D149" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E149" t="s">
         <v>17</v>
       </c>
       <c r="F149" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B150" t="s">
         <v>38</v>
       </c>
       <c r="C150" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D150" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E150" t="s">
         <v>15</v>
       </c>
       <c r="F150" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B151" t="s">
         <v>25</v>
       </c>
       <c r="C151" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D151" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E151" t="s">
         <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B152" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C152" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D152" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E152" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F152" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B153" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D153" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F153" t="s">
         <v>17</v>
@@ -4545,19 +4560,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B154" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C154" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D154" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E154" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F154" t="s">
         <v>27</v>
@@ -4565,39 +4580,39 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>233</v>
+      </c>
+      <c r="B155" t="s">
+        <v>237</v>
+      </c>
+      <c r="C155" t="s">
         <v>238</v>
       </c>
-      <c r="B155" t="s">
-        <v>242</v>
-      </c>
-      <c r="C155" t="s">
-        <v>243</v>
-      </c>
       <c r="D155" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E155" t="s">
         <v>31</v>
       </c>
       <c r="F155" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B156" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C156" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D156" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E156" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F156" t="s">
         <v>29</v>
@@ -4605,16 +4620,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B157" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C157" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D157" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -4625,16 +4640,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B158" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C158" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D158" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E158" t="s">
         <v>48</v>
@@ -4645,19 +4660,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B159" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C159" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D159" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E159" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F159" t="s">
         <v>58</v>
@@ -4665,16 +4680,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B160" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C160" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D160" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E160" t="s">
         <v>39</v>
@@ -4685,79 +4700,79 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B161" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C161" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D161" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E161" t="s">
         <v>31</v>
       </c>
       <c r="F161" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B162" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C162" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D162" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E162" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F162" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B163" t="s">
         <v>53</v>
       </c>
       <c r="C163" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D163" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E163" t="s">
         <v>39</v>
       </c>
       <c r="F163" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B164" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C164" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D164" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E164" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F164" t="s">
         <v>15</v>
@@ -4765,76 +4780,76 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B165" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C165" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D165" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E165" t="s">
         <v>59</v>
       </c>
       <c r="F165" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B166" t="s">
         <v>38</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D166" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E166" t="s">
         <v>15</v>
       </c>
       <c r="F166" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B167" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D167" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E167" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F167" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>250</v>
+      </c>
+      <c r="B168" t="s">
         <v>255</v>
       </c>
-      <c r="B168" t="s">
-        <v>260</v>
-      </c>
       <c r="C168" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D168" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E168" t="s">
         <v>17</v>
@@ -4845,139 +4860,139 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B169" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C169" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D169" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E169" t="s">
         <v>15</v>
       </c>
       <c r="F169" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B170" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C170" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D170" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E170" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F170" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B171" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C171" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E171" t="s">
         <v>49</v>
       </c>
       <c r="F171" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B172" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C172" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D172" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E172" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F172" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B173" t="s">
         <v>38</v>
       </c>
       <c r="C173" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E173" t="s">
         <v>15</v>
       </c>
       <c r="F173" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B174" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C174" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D174" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E174" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
       <c r="F174" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B175" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D175" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E175" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F175" t="s">
         <v>15</v>
@@ -4985,76 +5000,76 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B176" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C176" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D176" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E176" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F176" t="s">
-        <v>275</v>
+        <v>370</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B177" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C177" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D177" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E177" t="s">
         <v>17</v>
       </c>
       <c r="F177" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B178" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C178" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D178" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E178" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F178" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B179" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C179" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E179" t="s">
         <v>48</v>
@@ -5065,19 +5080,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B180" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C180" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D180" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E180" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F180" t="s">
         <v>27</v>
@@ -5085,79 +5100,79 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B181" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C181" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D181" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E181" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F181" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B182" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C182" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D182" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E182" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F182" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E183" t="s">
         <v>15</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="F184" t="s">
         <v>48</v>
@@ -5165,59 +5180,59 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E185" t="s">
         <v>15</v>
       </c>
       <c r="F185" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>29</v>
@@ -5225,59 +5240,59 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F188" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>289</v>
+        <v>372</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F190" t="s">
         <v>31</v>
@@ -5285,22 +5300,482 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>287</v>
+      </c>
+      <c r="B192" t="s">
+        <v>38</v>
+      </c>
+      <c r="C192" t="s">
+        <v>170</v>
+      </c>
+      <c r="D192" t="s">
+        <v>185</v>
+      </c>
+      <c r="E192" t="s">
+        <v>15</v>
+      </c>
+      <c r="F192" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>287</v>
+      </c>
+      <c r="B193" t="s">
+        <v>130</v>
+      </c>
+      <c r="C193" t="s">
+        <v>167</v>
+      </c>
+      <c r="D193" t="s">
+        <v>168</v>
+      </c>
+      <c r="E193" t="s">
+        <v>252</v>
+      </c>
+      <c r="F193" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>287</v>
+      </c>
+      <c r="B194" t="s">
+        <v>110</v>
+      </c>
+      <c r="C194" t="s">
+        <v>158</v>
+      </c>
+      <c r="D194" t="s">
+        <v>159</v>
+      </c>
+      <c r="E194" t="s">
+        <v>59</v>
+      </c>
+      <c r="F194" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>287</v>
+      </c>
+      <c r="B195" t="s">
+        <v>373</v>
+      </c>
+      <c r="C195" t="s">
+        <v>214</v>
+      </c>
+      <c r="D195" t="s">
+        <v>288</v>
+      </c>
+      <c r="E195" t="s">
+        <v>249</v>
+      </c>
+      <c r="F195" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>287</v>
+      </c>
+      <c r="B196" t="s">
+        <v>83</v>
+      </c>
+      <c r="C196" t="s">
+        <v>230</v>
+      </c>
+      <c r="D196" t="s">
+        <v>231</v>
+      </c>
+      <c r="E196" t="s">
+        <v>15</v>
+      </c>
+      <c r="F196" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>287</v>
+      </c>
+      <c r="B197" t="s">
+        <v>289</v>
+      </c>
+      <c r="C197" t="s">
+        <v>290</v>
+      </c>
+      <c r="D197" t="s">
+        <v>184</v>
+      </c>
+      <c r="E197" t="s">
+        <v>18</v>
+      </c>
+      <c r="F197" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>291</v>
+      </c>
+      <c r="B198" t="s">
+        <v>25</v>
+      </c>
+      <c r="C198" t="s">
+        <v>158</v>
+      </c>
+      <c r="D198" t="s">
+        <v>217</v>
+      </c>
+      <c r="E198" t="s">
+        <v>161</v>
+      </c>
+      <c r="F198" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>291</v>
+      </c>
+      <c r="B199" t="s">
+        <v>130</v>
+      </c>
+      <c r="C199" t="s">
+        <v>167</v>
+      </c>
+      <c r="D199" t="s">
+        <v>168</v>
+      </c>
+      <c r="E199" t="s">
+        <v>252</v>
+      </c>
+      <c r="F199" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>291</v>
+      </c>
+      <c r="B200" t="s">
+        <v>38</v>
+      </c>
+      <c r="C200" t="s">
+        <v>170</v>
+      </c>
+      <c r="D200" t="s">
+        <v>185</v>
+      </c>
+      <c r="E200" t="s">
+        <v>15</v>
+      </c>
+      <c r="F200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>291</v>
+      </c>
+      <c r="B201" t="s">
+        <v>281</v>
+      </c>
+      <c r="C201" t="s">
+        <v>222</v>
+      </c>
+      <c r="D201" t="s">
+        <v>282</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+      <c r="F201" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>291</v>
+      </c>
+      <c r="B202" t="s">
+        <v>293</v>
+      </c>
+      <c r="C202" t="s">
+        <v>294</v>
+      </c>
+      <c r="D202" t="s">
+        <v>184</v>
+      </c>
+      <c r="E202" t="s">
+        <v>39</v>
+      </c>
+      <c r="F202" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>291</v>
+      </c>
+      <c r="B203" t="s">
+        <v>374</v>
+      </c>
+      <c r="C203" t="s">
+        <v>214</v>
+      </c>
+      <c r="D203" t="s">
+        <v>230</v>
+      </c>
+      <c r="E203" t="s">
+        <v>76</v>
+      </c>
+      <c r="F203" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>291</v>
+      </c>
+      <c r="B204" t="s">
+        <v>295</v>
+      </c>
+      <c r="C204" t="s">
+        <v>296</v>
+      </c>
+      <c r="D204" t="s">
+        <v>297</v>
+      </c>
+      <c r="E204" t="s">
+        <v>48</v>
+      </c>
+      <c r="F204" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>291</v>
+      </c>
+      <c r="B205" t="s">
+        <v>298</v>
+      </c>
+      <c r="C205" t="s">
+        <v>299</v>
+      </c>
+      <c r="D205" t="s">
+        <v>300</v>
+      </c>
+      <c r="E205" t="s">
+        <v>375</v>
+      </c>
+      <c r="F205" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>301</v>
+      </c>
+      <c r="B206" t="s">
+        <v>38</v>
+      </c>
+      <c r="C206" t="s">
+        <v>170</v>
+      </c>
+      <c r="D206" t="s">
+        <v>185</v>
+      </c>
+      <c r="E206" t="s">
+        <v>15</v>
+      </c>
+      <c r="F206" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>301</v>
+      </c>
+      <c r="B207" t="s">
+        <v>130</v>
+      </c>
+      <c r="C207" t="s">
+        <v>167</v>
+      </c>
+      <c r="D207" t="s">
+        <v>168</v>
+      </c>
+      <c r="E207" t="s">
+        <v>252</v>
+      </c>
+      <c r="F207" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>301</v>
+      </c>
+      <c r="B208" t="s">
+        <v>302</v>
+      </c>
+      <c r="C208" t="s">
+        <v>230</v>
+      </c>
+      <c r="D208" t="s">
+        <v>214</v>
+      </c>
+      <c r="E208" t="s">
+        <v>17</v>
+      </c>
+      <c r="F208" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>301</v>
+      </c>
+      <c r="B209" t="s">
+        <v>25</v>
+      </c>
+      <c r="C209" t="s">
+        <v>158</v>
+      </c>
+      <c r="D209" t="s">
+        <v>217</v>
+      </c>
+      <c r="E209" t="s">
+        <v>15</v>
+      </c>
+      <c r="F209" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>301</v>
+      </c>
+      <c r="B210" t="s">
+        <v>303</v>
+      </c>
+      <c r="C210" t="s">
+        <v>184</v>
+      </c>
+      <c r="D210" t="s">
+        <v>294</v>
+      </c>
+      <c r="E210" t="s">
+        <v>15</v>
+      </c>
+      <c r="F210" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>301</v>
+      </c>
+      <c r="B211" t="s">
+        <v>304</v>
+      </c>
+      <c r="C211" t="s">
+        <v>305</v>
+      </c>
+      <c r="D211" t="s">
+        <v>306</v>
+      </c>
+      <c r="E211" t="s">
+        <v>49</v>
+      </c>
+      <c r="F211" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>301</v>
+      </c>
+      <c r="B212" t="s">
+        <v>307</v>
+      </c>
+      <c r="C212" t="s">
+        <v>191</v>
+      </c>
+      <c r="D212" t="s">
+        <v>308</v>
+      </c>
+      <c r="E212" t="s">
+        <v>232</v>
+      </c>
+      <c r="F212" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>301</v>
+      </c>
+      <c r="B213" t="s">
+        <v>309</v>
+      </c>
+      <c r="C213" t="s">
+        <v>257</v>
+      </c>
+      <c r="D213" t="s">
+        <v>256</v>
+      </c>
+      <c r="E213" t="s">
+        <v>27</v>
+      </c>
+      <c r="F213" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>301</v>
+      </c>
+      <c r="B214" t="s">
+        <v>310</v>
+      </c>
+      <c r="C214" t="s">
+        <v>197</v>
+      </c>
+      <c r="D214" t="s">
+        <v>271</v>
+      </c>
+      <c r="E214" t="s">
+        <v>48</v>
+      </c>
+      <c r="F214" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -5347,19 +5822,19 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5367,19 +5842,19 @@
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5390,16 +5865,16 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5407,19 +5882,19 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5427,19 +5902,19 @@
         <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
         <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5450,16 +5925,16 @@
         <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5467,19 +5942,19 @@
         <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5487,19 +5962,19 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5507,19 +5982,19 @@
         <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5527,19 +6002,19 @@
         <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F11" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5547,19 +6022,19 @@
         <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
